--- a/assets/constructions/examples/ctd_jse_m.xlsx
+++ b/assets/constructions/examples/ctd_jse_m.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ctd" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ctd" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AR6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -649,31 +649,56 @@
           <t>releasepack</t>
         </is>
       </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>lcs</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>pricecurrency</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue_rub</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>M12x1.75 2620-1515.2 Р6М5 ГОСТ 3266-81 с покрытием</t>
+          <t>TE403326</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>ТИЗ</t>
+          <t>YG1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ММГП 3266</t>
+          <t>TE403</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>PK</t>
+          <t>K</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>MN</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -683,46 +708,54 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Coarse</t>
+          <t>Fine</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>ISO 2</t>
+          <t>6HX</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>6</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>M12</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr"/>
+          <t>M6x0.75</t>
+        </is>
+      </c>
+      <c r="L2" t="n">
+        <v>5.2</v>
+      </c>
       <c r="M2" t="n">
-        <v>1.75</v>
+        <v>0.75</v>
       </c>
       <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="P2" t="n">
+        <v>4</v>
+      </c>
       <c r="Q2" t="n">
-        <v>9</v>
+        <v>4.5</v>
       </c>
       <c r="R2" t="inlineStr"/>
       <c r="S2" t="n">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="T2" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="U2" t="n">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -737,7 +770,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>DCON_X_DRVS:9X7.1</t>
+          <t>DCON_X_DRVS:4.5x3.4</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
@@ -749,19 +782,19 @@
         <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>7.1</v>
+        <v>3.4</v>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>TIN</t>
-        </is>
-      </c>
-      <c r="AD2" t="inlineStr"/>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>Р6М5</t>
-        </is>
-      </c>
+          <t>Nitride (NI)</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>HSS-E</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr"/>
       <c r="AF2" t="inlineStr">
         <is>
           <t>HSS</t>
@@ -780,18 +813,14 @@
           <t>N</t>
         </is>
       </c>
-      <c r="AJ2" t="n">
-        <v>17</v>
-      </c>
+      <c r="AJ2" t="inlineStr"/>
       <c r="AK2" t="inlineStr"/>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>ГОСТ 3266-81</t>
-        </is>
-      </c>
-      <c r="AM2" t="n">
-        <v>12</v>
-      </c>
+          <t>DIN 374</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr"/>
       <c r="AN2" t="inlineStr"/>
       <c r="AO2" t="n">
         <v>0</v>
@@ -801,88 +830,107 @@
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>BLIND</t>
+          <t>BOTH</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>2019/ТИЗ каталог общепромышленного инструмента</t>
+          <t>2025 / YG1 Нарезание резьбы</t>
+        </is>
+      </c>
+      <c r="AS2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>25.44</v>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AV2" t="n">
+        <v>2338.79</v>
+      </c>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>KN</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>401440NC632</t>
+          <t>M20x1.5 2620-1716.3 Р6М5 ГОСТ 3266-81</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>HELION</t>
+          <t>ТИЗ</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>40.1440</t>
+          <t>ММГП 3266</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>MK</t>
+          <t>PKN</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>M</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>UN60</t>
+          <t>M60</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Coarse</t>
+          <t>Fine</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2B</t>
+          <t>6G</t>
         </is>
       </c>
       <c r="I3" t="n">
-        <v>3.51</v>
+        <v>20</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>3.51</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>#6 - 32 UNC</t>
-        </is>
-      </c>
-      <c r="L3" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="n">
-        <v>32</v>
-      </c>
+          <t>M20x1.5</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr"/>
       <c r="Q3" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="R3" t="inlineStr"/>
-      <c r="S3" t="inlineStr"/>
+      <c r="S3" t="n">
+        <v>37</v>
+      </c>
       <c r="T3" t="n">
-        <v>12</v>
+        <v>37</v>
       </c>
       <c r="U3" t="n">
-        <v>56</v>
+        <v>112</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -892,12 +940,12 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>DCON_X_DRVS:4x2.85</t>
+          <t>DCON_X_DRVS:14x11.2</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -905,23 +953,21 @@
           <t>WORKPIECE</t>
         </is>
       </c>
-      <c r="AA3" t="inlineStr"/>
+      <c r="AA3" t="b">
+        <v>0</v>
+      </c>
       <c r="AB3" t="n">
-        <v>2.85</v>
+        <v>11.2</v>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>BLACK HVA</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>HSS-E</t>
-        </is>
-      </c>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr"/>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>HSS-E</t>
+          <t>Р6М5</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
@@ -942,53 +988,76 @@
           <t>N</t>
         </is>
       </c>
-      <c r="AJ3" t="inlineStr"/>
+      <c r="AJ3" t="n">
+        <v>22</v>
+      </c>
       <c r="AK3" t="inlineStr"/>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>DIN 371/376</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr"/>
+          <t>ГОСТ 3266-81</t>
+        </is>
+      </c>
+      <c r="AM3" t="n">
+        <v>12</v>
+      </c>
       <c r="AN3" t="inlineStr"/>
-      <c r="AO3" t="inlineStr"/>
-      <c r="AP3" t="inlineStr"/>
+      <c r="AO3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP3" t="b">
+        <v>0</v>
+      </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>THROUGH</t>
+          <t>BLIND</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>HELION Основной каталог 2023 ENG</t>
+          <t>2019/ТИЗ каталог общепромышленного инструмента</t>
+        </is>
+      </c>
+      <c r="AS3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AU3" t="inlineStr"/>
+      <c r="AV3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>PMKN</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>TAP 3/4-10 UNC A 19 S 2B HSSE TiX2</t>
+          <t>GX355102 WK12PG</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>VERGNANO</t>
+          <t>WIDIA</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>A19 S</t>
+          <t>GX35</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>PM</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr"/>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>UN60</t>
+          <t>M60</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -998,55 +1067,57 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2B</t>
+          <t>6HX</t>
         </is>
       </c>
       <c r="I4" t="n">
-        <v>19.05</v>
+        <v>10</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>3/4</t>
+          <t>10</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>3/4" - 10 UNC</t>
-        </is>
-      </c>
-      <c r="L4" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="n">
-        <v>10</v>
-      </c>
-      <c r="O4" t="inlineStr"/>
+          <t>M10x1.25</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
       <c r="P4" t="n">
         <v>4</v>
       </c>
       <c r="Q4" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>h9</t>
+          <t>h6</t>
         </is>
       </c>
       <c r="S4" t="n">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="T4" t="n">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="U4" t="n">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
@@ -1055,7 +1126,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>DCON_X_DRVS:14X11</t>
+          <t>DCON_X_DRVS:7x5.5</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1063,20 +1134,26 @@
           <t>WORKPIECE</t>
         </is>
       </c>
-      <c r="AA4" t="inlineStr"/>
+      <c r="AA4" t="b">
+        <v>0</v>
+      </c>
       <c r="AB4" t="n">
-        <v>11</v>
+        <v>5.5</v>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>TIX2</t>
+          <t>TiCN</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr"/>
-      <c r="AE4" t="inlineStr"/>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>WK12PG</t>
+        </is>
+      </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>HSS</t>
+          <t>VHM</t>
         </is>
       </c>
       <c r="AG4" t="n">
@@ -1092,52 +1169,67 @@
           <t>N</t>
         </is>
       </c>
-      <c r="AJ4" t="inlineStr"/>
+      <c r="AJ4" t="n">
+        <v>61</v>
+      </c>
       <c r="AK4" t="inlineStr"/>
-      <c r="AL4" t="inlineStr">
-        <is>
-          <t>DIN 2184-1</t>
-        </is>
-      </c>
+      <c r="AL4" t="inlineStr"/>
       <c r="AM4" t="inlineStr"/>
       <c r="AN4" t="inlineStr"/>
       <c r="AO4" t="n">
         <v>0</v>
       </c>
-      <c r="AP4" t="inlineStr"/>
+      <c r="AP4" t="b">
+        <v>0</v>
+      </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>THROUGH</t>
+          <t>BLIND</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>2022/Vergnano-General-Catalog-76.pdf</t>
+          <t>2015 / Widia Твердосплавные метчики GTD RU</t>
+        </is>
+      </c>
+      <c r="AS4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AU4" t="inlineStr"/>
+      <c r="AV4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>PK</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>TAP M 20x2,5 BP 29 HSSP TiH1</t>
+          <t>M20x2.5 2621-1729.3 Р6М5 ГОСТ 3266-81</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>VERGNANO</t>
+          <t>ТИЗ</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>BP29TiH1</t>
+          <t>ММСП 3266</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>PKNS</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr"/>
+          <t>PKN</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
       <c r="F5" t="inlineStr">
         <is>
           <t>M60</t>
@@ -1150,7 +1242,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>6HX</t>
+          <t>6G</t>
         </is>
       </c>
       <c r="I5" t="n">
@@ -1163,44 +1255,34 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>M20</t>
-        </is>
-      </c>
-      <c r="L5" t="n">
-        <v>17.5</v>
-      </c>
+          <t>M20x2.5</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr"/>
       <c r="M5" t="n">
         <v>2.5</v>
       </c>
       <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="P5" t="n">
-        <v>4</v>
-      </c>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
       <c r="Q5" t="n">
-        <v>16</v>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>h9</t>
-        </is>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="R5" t="inlineStr"/>
       <c r="S5" t="n">
-        <v>20</v>
-      </c>
-      <c r="T5" t="inlineStr"/>
+        <v>37</v>
+      </c>
+      <c r="T5" t="n">
+        <v>37</v>
+      </c>
       <c r="U5" t="n">
-        <v>140</v>
+        <v>112</v>
       </c>
       <c r="V5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
@@ -1209,7 +1291,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>DCON_X_DRVS:16X12</t>
+          <t>DCON_X_DRVS:14x11.2</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1221,30 +1303,26 @@
         <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>12</v>
+        <v>11.2</v>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>TiH1</t>
-        </is>
-      </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>HSSP</t>
-        </is>
-      </c>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr"/>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>HSSP</t>
+          <t>Р6М5</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>PME</t>
+          <t>HSS</t>
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1253,58 +1331,79 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr"/>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AJ5" t="n">
+        <v>22</v>
+      </c>
       <c r="AK5" t="inlineStr"/>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>DIN 371</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr"/>
+          <t>ГОСТ 3266-81</t>
+        </is>
+      </c>
+      <c r="AM5" t="n">
+        <v>6</v>
+      </c>
       <c r="AN5" t="inlineStr"/>
-      <c r="AO5" t="inlineStr"/>
+      <c r="AO5" t="n">
+        <v>0</v>
+      </c>
       <c r="AP5" t="b">
         <v>0</v>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>BLIND</t>
+          <t>THROUGH</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>2020 / Vergnano Catalog</t>
+          <t>2019/ТИЗ каталог общепромышленного инструмента</t>
+        </is>
+      </c>
+      <c r="AS5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AU5" t="inlineStr"/>
+      <c r="AV5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>PMKN</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>N360-3 UNF1/4-28 2B</t>
+          <t>M22x1 2621-1754.3 Р18 ГОСТ 3266-81 с покрытием</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>DC SWISS</t>
+          <t>ТИЗ</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>N360-3</t>
+          <t>ММСП 3266</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr"/>
+          <t>MS</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>PKN</t>
+        </is>
+      </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>UN60</t>
+          <t>M60</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1314,66 +1413,56 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2B</t>
+          <t>6G</t>
         </is>
       </c>
       <c r="I6" t="n">
-        <v>0.25</v>
+        <v>22</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>1/4</t>
+          <t>22</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>1/4" - 28 UNF</t>
-        </is>
-      </c>
-      <c r="L6" t="n">
-        <v>5.5</v>
-      </c>
+          <t>M22x1</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr"/>
       <c r="M6" t="n">
-        <v>0.907</v>
-      </c>
-      <c r="N6" t="n">
-        <v>28</v>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="P6" t="n">
-        <v>3</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
       <c r="Q6" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="n">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="T6" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="U6" t="n">
-        <v>80</v>
+        <v>112</v>
       </c>
       <c r="V6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>DCON_X_DRVS:7X5.5</t>
+          <t>DCON_X_DRVS:16x12.5</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1385,26 +1474,26 @@
         <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>5.5</v>
+        <v>12.5</v>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>TIN</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr"/>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>Р18</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>PME</t>
+          <t>HSS</t>
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1413,30 +1502,47 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="AJ6" t="inlineStr"/>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AJ6" t="n">
+        <v>24</v>
+      </c>
       <c r="AK6" t="inlineStr"/>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>DIN 371</t>
-        </is>
-      </c>
-      <c r="AM6" t="inlineStr"/>
+          <t>ГОСТ 3266-81</t>
+        </is>
+      </c>
+      <c r="AM6" t="n">
+        <v>6</v>
+      </c>
       <c r="AN6" t="inlineStr"/>
-      <c r="AO6" t="inlineStr"/>
+      <c r="AO6" t="n">
+        <v>0</v>
+      </c>
       <c r="AP6" t="b">
         <v>0</v>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>BLIND</t>
+          <t>THROUGH</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>2020 / DC Swiss website</t>
+          <t>2019/ТИЗ каталог общепромышленного инструмента</t>
+        </is>
+      </c>
+      <c r="AS6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AU6" t="inlineStr"/>
+      <c r="AV6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>PMKNS</t>
         </is>
       </c>
     </row>
